--- a/docs/RMD2_Variables-y-Metricas-Completas.xlsx
+++ b/docs/RMD2_Variables-y-Metricas-Completas.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexis/Desktop/Go en Conflictos/RMD 2.0/RMD/docs/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABD14E9-6C6F-DE48-8398-2A53A521F410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="20" windowWidth="47840" windowHeight="24760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -13825,8 +13831,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13889,13 +13895,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -13933,7 +13947,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -13967,6 +13981,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -14001,9 +14016,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -14176,11 +14192,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U311"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="50.83203125" customWidth="1"/>
+    <col min="3" max="3" width="58.83203125" customWidth="1"/>
+    <col min="9" max="9" width="47.5" customWidth="1"/>
+    <col min="10" max="10" width="29.83203125" customWidth="1"/>
+    <col min="11" max="11" width="49.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14245,7 +14268,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -14310,7 +14333,7 @@
         <v>4302</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -14375,7 +14398,7 @@
         <v>4303</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -14440,7 +14463,7 @@
         <v>4304</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -14505,7 +14528,7 @@
         <v>4305</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -14570,7 +14593,7 @@
         <v>4306</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -14635,7 +14658,7 @@
         <v>4307</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -14700,7 +14723,7 @@
         <v>4308</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -14765,7 +14788,7 @@
         <v>4309</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -14830,7 +14853,7 @@
         <v>4310</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -14895,7 +14918,7 @@
         <v>4311</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -14960,7 +14983,7 @@
         <v>4312</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -15025,7 +15048,7 @@
         <v>4313</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -15090,7 +15113,7 @@
         <v>4314</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -15155,7 +15178,7 @@
         <v>4315</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -15220,7 +15243,7 @@
         <v>4316</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -15285,7 +15308,7 @@
         <v>4317</v>
       </c>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -15350,7 +15373,7 @@
         <v>4318</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -15415,7 +15438,7 @@
         <v>4319</v>
       </c>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -15480,7 +15503,7 @@
         <v>4320</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -15545,7 +15568,7 @@
         <v>4321</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -15610,7 +15633,7 @@
         <v>4322</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -15675,7 +15698,7 @@
         <v>4323</v>
       </c>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -15740,7 +15763,7 @@
         <v>4324</v>
       </c>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -15805,7 +15828,7 @@
         <v>4325</v>
       </c>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -15870,7 +15893,7 @@
         <v>4326</v>
       </c>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -15935,7 +15958,7 @@
         <v>4327</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -16000,7 +16023,7 @@
         <v>4328</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -16065,7 +16088,7 @@
         <v>4329</v>
       </c>
     </row>
-    <row r="30" spans="1:21">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -16130,7 +16153,7 @@
         <v>4330</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -16195,7 +16218,7 @@
         <v>4331</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -16260,7 +16283,7 @@
         <v>4332</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -16325,7 +16348,7 @@
         <v>4333</v>
       </c>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -16390,7 +16413,7 @@
         <v>4334</v>
       </c>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -16455,7 +16478,7 @@
         <v>4335</v>
       </c>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -16520,7 +16543,7 @@
         <v>4336</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -16585,7 +16608,7 @@
         <v>4337</v>
       </c>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -16650,7 +16673,7 @@
         <v>4338</v>
       </c>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -16715,7 +16738,7 @@
         <v>4339</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -16780,7 +16803,7 @@
         <v>4340</v>
       </c>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -16845,7 +16868,7 @@
         <v>4341</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -16910,7 +16933,7 @@
         <v>4342</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -16975,7 +16998,7 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="44" spans="1:21">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -17040,7 +17063,7 @@
         <v>4344</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -17105,7 +17128,7 @@
         <v>4345</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -17170,7 +17193,7 @@
         <v>4346</v>
       </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -17235,7 +17258,7 @@
         <v>4347</v>
       </c>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -17300,7 +17323,7 @@
         <v>4348</v>
       </c>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -17365,7 +17388,7 @@
         <v>4349</v>
       </c>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -17430,7 +17453,7 @@
         <v>4350</v>
       </c>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -17495,7 +17518,7 @@
         <v>4351</v>
       </c>
     </row>
-    <row r="52" spans="1:21">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -17560,7 +17583,7 @@
         <v>4352</v>
       </c>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -17625,7 +17648,7 @@
         <v>4353</v>
       </c>
     </row>
-    <row r="54" spans="1:21">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -17690,7 +17713,7 @@
         <v>4354</v>
       </c>
     </row>
-    <row r="55" spans="1:21">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -17755,7 +17778,7 @@
         <v>4355</v>
       </c>
     </row>
-    <row r="56" spans="1:21">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -17820,7 +17843,7 @@
         <v>4356</v>
       </c>
     </row>
-    <row r="57" spans="1:21">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -17885,7 +17908,7 @@
         <v>4357</v>
       </c>
     </row>
-    <row r="58" spans="1:21">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -17950,7 +17973,7 @@
         <v>4358</v>
       </c>
     </row>
-    <row r="59" spans="1:21">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -18015,7 +18038,7 @@
         <v>4359</v>
       </c>
     </row>
-    <row r="60" spans="1:21">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -18080,7 +18103,7 @@
         <v>4360</v>
       </c>
     </row>
-    <row r="61" spans="1:21">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -18145,7 +18168,7 @@
         <v>4361</v>
       </c>
     </row>
-    <row r="62" spans="1:21">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -18210,7 +18233,7 @@
         <v>4362</v>
       </c>
     </row>
-    <row r="63" spans="1:21">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -18275,7 +18298,7 @@
         <v>4359</v>
       </c>
     </row>
-    <row r="64" spans="1:21">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -18340,7 +18363,7 @@
         <v>4363</v>
       </c>
     </row>
-    <row r="65" spans="1:21">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -18405,7 +18428,7 @@
         <v>4323</v>
       </c>
     </row>
-    <row r="66" spans="1:21">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -18470,7 +18493,7 @@
         <v>4364</v>
       </c>
     </row>
-    <row r="67" spans="1:21">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -18535,7 +18558,7 @@
         <v>4365</v>
       </c>
     </row>
-    <row r="68" spans="1:21">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -18600,7 +18623,7 @@
         <v>4366</v>
       </c>
     </row>
-    <row r="69" spans="1:21">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -18665,7 +18688,7 @@
         <v>4367</v>
       </c>
     </row>
-    <row r="70" spans="1:21">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -18730,7 +18753,7 @@
         <v>4368</v>
       </c>
     </row>
-    <row r="71" spans="1:21">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -18795,7 +18818,7 @@
         <v>4369</v>
       </c>
     </row>
-    <row r="72" spans="1:21">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -18860,7 +18883,7 @@
         <v>4370</v>
       </c>
     </row>
-    <row r="73" spans="1:21">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -18925,7 +18948,7 @@
         <v>4371</v>
       </c>
     </row>
-    <row r="74" spans="1:21">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -18990,7 +19013,7 @@
         <v>4311</v>
       </c>
     </row>
-    <row r="75" spans="1:21">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -19055,7 +19078,7 @@
         <v>4372</v>
       </c>
     </row>
-    <row r="76" spans="1:21">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -19120,7 +19143,7 @@
         <v>4373</v>
       </c>
     </row>
-    <row r="77" spans="1:21">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -19185,7 +19208,7 @@
         <v>4321</v>
       </c>
     </row>
-    <row r="78" spans="1:21">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -19250,7 +19273,7 @@
         <v>4374</v>
       </c>
     </row>
-    <row r="79" spans="1:21">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -19315,7 +19338,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="80" spans="1:21">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -19380,7 +19403,7 @@
         <v>4376</v>
       </c>
     </row>
-    <row r="81" spans="1:21">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -19445,7 +19468,7 @@
         <v>4377</v>
       </c>
     </row>
-    <row r="82" spans="1:21">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -19510,7 +19533,7 @@
         <v>4378</v>
       </c>
     </row>
-    <row r="83" spans="1:21">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -19575,7 +19598,7 @@
         <v>4379</v>
       </c>
     </row>
-    <row r="84" spans="1:21">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -19640,7 +19663,7 @@
         <v>4380</v>
       </c>
     </row>
-    <row r="85" spans="1:21">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -19705,7 +19728,7 @@
         <v>4381</v>
       </c>
     </row>
-    <row r="86" spans="1:21">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -19770,7 +19793,7 @@
         <v>4382</v>
       </c>
     </row>
-    <row r="87" spans="1:21">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -19835,7 +19858,7 @@
         <v>4383</v>
       </c>
     </row>
-    <row r="88" spans="1:21">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -19900,7 +19923,7 @@
         <v>4384</v>
       </c>
     </row>
-    <row r="89" spans="1:21">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -19965,7 +19988,7 @@
         <v>4385</v>
       </c>
     </row>
-    <row r="90" spans="1:21">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -20030,7 +20053,7 @@
         <v>4386</v>
       </c>
     </row>
-    <row r="91" spans="1:21">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -20095,7 +20118,7 @@
         <v>4387</v>
       </c>
     </row>
-    <row r="92" spans="1:21">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -20160,7 +20183,7 @@
         <v>4388</v>
       </c>
     </row>
-    <row r="93" spans="1:21">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -20225,7 +20248,7 @@
         <v>4389</v>
       </c>
     </row>
-    <row r="94" spans="1:21">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -20290,7 +20313,7 @@
         <v>4390</v>
       </c>
     </row>
-    <row r="95" spans="1:21">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -20355,7 +20378,7 @@
         <v>4391</v>
       </c>
     </row>
-    <row r="96" spans="1:21">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -20420,7 +20443,7 @@
         <v>4392</v>
       </c>
     </row>
-    <row r="97" spans="1:21">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -20485,7 +20508,7 @@
         <v>4393</v>
       </c>
     </row>
-    <row r="98" spans="1:21">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -20550,7 +20573,7 @@
         <v>4394</v>
       </c>
     </row>
-    <row r="99" spans="1:21">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -20615,7 +20638,7 @@
         <v>4395</v>
       </c>
     </row>
-    <row r="100" spans="1:21">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -20680,7 +20703,7 @@
         <v>4396</v>
       </c>
     </row>
-    <row r="101" spans="1:21">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -20745,7 +20768,7 @@
         <v>4397</v>
       </c>
     </row>
-    <row r="102" spans="1:21">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -20810,7 +20833,7 @@
         <v>4398</v>
       </c>
     </row>
-    <row r="103" spans="1:21">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -20875,7 +20898,7 @@
         <v>4399</v>
       </c>
     </row>
-    <row r="104" spans="1:21">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -20940,7 +20963,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="105" spans="1:21">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -21005,7 +21028,7 @@
         <v>4401</v>
       </c>
     </row>
-    <row r="106" spans="1:21">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -21070,7 +21093,7 @@
         <v>4402</v>
       </c>
     </row>
-    <row r="107" spans="1:21">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -21135,7 +21158,7 @@
         <v>4403</v>
       </c>
     </row>
-    <row r="108" spans="1:21">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
@@ -21200,7 +21223,7 @@
         <v>4404</v>
       </c>
     </row>
-    <row r="109" spans="1:21">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -21265,7 +21288,7 @@
         <v>4405</v>
       </c>
     </row>
-    <row r="110" spans="1:21">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
@@ -21330,7 +21353,7 @@
         <v>4406</v>
       </c>
     </row>
-    <row r="111" spans="1:21">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -21395,7 +21418,7 @@
         <v>4407</v>
       </c>
     </row>
-    <row r="112" spans="1:21">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>
@@ -21460,7 +21483,7 @@
         <v>4408</v>
       </c>
     </row>
-    <row r="113" spans="1:21">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>112</v>
       </c>
@@ -21525,7 +21548,7 @@
         <v>4409</v>
       </c>
     </row>
-    <row r="114" spans="1:21">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>113</v>
       </c>
@@ -21590,7 +21613,7 @@
         <v>4410</v>
       </c>
     </row>
-    <row r="115" spans="1:21">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>114</v>
       </c>
@@ -21655,7 +21678,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="116" spans="1:21">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>115</v>
       </c>
@@ -21720,7 +21743,7 @@
         <v>4412</v>
       </c>
     </row>
-    <row r="117" spans="1:21">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>116</v>
       </c>
@@ -21785,7 +21808,7 @@
         <v>4413</v>
       </c>
     </row>
-    <row r="118" spans="1:21">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>117</v>
       </c>
@@ -21850,7 +21873,7 @@
         <v>4414</v>
       </c>
     </row>
-    <row r="119" spans="1:21">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>118</v>
       </c>
@@ -21915,7 +21938,7 @@
         <v>4415</v>
       </c>
     </row>
-    <row r="120" spans="1:21">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>119</v>
       </c>
@@ -21980,7 +22003,7 @@
         <v>4416</v>
       </c>
     </row>
-    <row r="121" spans="1:21">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>120</v>
       </c>
@@ -22045,7 +22068,7 @@
         <v>4417</v>
       </c>
     </row>
-    <row r="122" spans="1:21">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>121</v>
       </c>
@@ -22110,7 +22133,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="123" spans="1:21">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>122</v>
       </c>
@@ -22175,7 +22198,7 @@
         <v>4419</v>
       </c>
     </row>
-    <row r="124" spans="1:21">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>123</v>
       </c>
@@ -22240,7 +22263,7 @@
         <v>4420</v>
       </c>
     </row>
-    <row r="125" spans="1:21">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>124</v>
       </c>
@@ -22305,7 +22328,7 @@
         <v>4421</v>
       </c>
     </row>
-    <row r="126" spans="1:21">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>125</v>
       </c>
@@ -22370,7 +22393,7 @@
         <v>4422</v>
       </c>
     </row>
-    <row r="127" spans="1:21">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>126</v>
       </c>
@@ -22435,7 +22458,7 @@
         <v>4423</v>
       </c>
     </row>
-    <row r="128" spans="1:21">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>127</v>
       </c>
@@ -22500,7 +22523,7 @@
         <v>4424</v>
       </c>
     </row>
-    <row r="129" spans="1:21">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>128</v>
       </c>
@@ -22565,7 +22588,7 @@
         <v>4425</v>
       </c>
     </row>
-    <row r="130" spans="1:21">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>129</v>
       </c>
@@ -22630,7 +22653,7 @@
         <v>4426</v>
       </c>
     </row>
-    <row r="131" spans="1:21">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>130</v>
       </c>
@@ -22695,7 +22718,7 @@
         <v>4427</v>
       </c>
     </row>
-    <row r="132" spans="1:21">
+    <row r="132" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>131</v>
       </c>
@@ -22760,7 +22783,7 @@
         <v>4428</v>
       </c>
     </row>
-    <row r="133" spans="1:21">
+    <row r="133" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>132</v>
       </c>
@@ -22825,7 +22848,7 @@
         <v>4429</v>
       </c>
     </row>
-    <row r="134" spans="1:21">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>133</v>
       </c>
@@ -22890,7 +22913,7 @@
         <v>4422</v>
       </c>
     </row>
-    <row r="135" spans="1:21">
+    <row r="135" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>134</v>
       </c>
@@ -22955,7 +22978,7 @@
         <v>4430</v>
       </c>
     </row>
-    <row r="136" spans="1:21">
+    <row r="136" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>135</v>
       </c>
@@ -23020,7 +23043,7 @@
         <v>4431</v>
       </c>
     </row>
-    <row r="137" spans="1:21">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>136</v>
       </c>
@@ -23085,7 +23108,7 @@
         <v>4432</v>
       </c>
     </row>
-    <row r="138" spans="1:21">
+    <row r="138" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>137</v>
       </c>
@@ -23150,7 +23173,7 @@
         <v>4433</v>
       </c>
     </row>
-    <row r="139" spans="1:21">
+    <row r="139" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>138</v>
       </c>
@@ -23215,7 +23238,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="140" spans="1:21">
+    <row r="140" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>139</v>
       </c>
@@ -23280,7 +23303,7 @@
         <v>4435</v>
       </c>
     </row>
-    <row r="141" spans="1:21">
+    <row r="141" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>140</v>
       </c>
@@ -23345,7 +23368,7 @@
         <v>4429</v>
       </c>
     </row>
-    <row r="142" spans="1:21">
+    <row r="142" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>141</v>
       </c>
@@ -23410,7 +23433,7 @@
         <v>4436</v>
       </c>
     </row>
-    <row r="143" spans="1:21">
+    <row r="143" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>142</v>
       </c>
@@ -23475,7 +23498,7 @@
         <v>4437</v>
       </c>
     </row>
-    <row r="144" spans="1:21">
+    <row r="144" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>143</v>
       </c>
@@ -23540,7 +23563,7 @@
         <v>4438</v>
       </c>
     </row>
-    <row r="145" spans="1:21">
+    <row r="145" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>144</v>
       </c>
@@ -23605,7 +23628,7 @@
         <v>4439</v>
       </c>
     </row>
-    <row r="146" spans="1:21">
+    <row r="146" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>145</v>
       </c>
@@ -23670,7 +23693,7 @@
         <v>4440</v>
       </c>
     </row>
-    <row r="147" spans="1:21">
+    <row r="147" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>146</v>
       </c>
@@ -23735,7 +23758,7 @@
         <v>4441</v>
       </c>
     </row>
-    <row r="148" spans="1:21">
+    <row r="148" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>147</v>
       </c>
@@ -23800,7 +23823,7 @@
         <v>4442</v>
       </c>
     </row>
-    <row r="149" spans="1:21">
+    <row r="149" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>148</v>
       </c>
@@ -23865,7 +23888,7 @@
         <v>4443</v>
       </c>
     </row>
-    <row r="150" spans="1:21">
+    <row r="150" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>149</v>
       </c>
@@ -23930,7 +23953,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="151" spans="1:21">
+    <row r="151" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>150</v>
       </c>
@@ -23995,7 +24018,7 @@
         <v>4445</v>
       </c>
     </row>
-    <row r="152" spans="1:21">
+    <row r="152" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>151</v>
       </c>
@@ -24060,7 +24083,7 @@
         <v>4446</v>
       </c>
     </row>
-    <row r="153" spans="1:21">
+    <row r="153" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>152</v>
       </c>
@@ -24125,7 +24148,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="154" spans="1:21">
+    <row r="154" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>153</v>
       </c>
@@ -24190,7 +24213,7 @@
         <v>4448</v>
       </c>
     </row>
-    <row r="155" spans="1:21">
+    <row r="155" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>154</v>
       </c>
@@ -24255,7 +24278,7 @@
         <v>4449</v>
       </c>
     </row>
-    <row r="156" spans="1:21">
+    <row r="156" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>155</v>
       </c>
@@ -24320,7 +24343,7 @@
         <v>4450</v>
       </c>
     </row>
-    <row r="157" spans="1:21">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>156</v>
       </c>
@@ -24385,7 +24408,7 @@
         <v>4451</v>
       </c>
     </row>
-    <row r="158" spans="1:21">
+    <row r="158" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>157</v>
       </c>
@@ -24450,7 +24473,7 @@
         <v>4452</v>
       </c>
     </row>
-    <row r="159" spans="1:21">
+    <row r="159" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>158</v>
       </c>
@@ -24515,7 +24538,7 @@
         <v>4453</v>
       </c>
     </row>
-    <row r="160" spans="1:21">
+    <row r="160" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>159</v>
       </c>
@@ -24580,7 +24603,7 @@
         <v>4454</v>
       </c>
     </row>
-    <row r="161" spans="1:21">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>160</v>
       </c>
@@ -24645,7 +24668,7 @@
         <v>4455</v>
       </c>
     </row>
-    <row r="162" spans="1:21">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>161</v>
       </c>
@@ -24710,7 +24733,7 @@
         <v>4456</v>
       </c>
     </row>
-    <row r="163" spans="1:21">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>162</v>
       </c>
@@ -24775,7 +24798,7 @@
         <v>4457</v>
       </c>
     </row>
-    <row r="164" spans="1:21">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>163</v>
       </c>
@@ -24840,7 +24863,7 @@
         <v>4458</v>
       </c>
     </row>
-    <row r="165" spans="1:21">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>164</v>
       </c>
@@ -24905,7 +24928,7 @@
         <v>4459</v>
       </c>
     </row>
-    <row r="166" spans="1:21">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>165</v>
       </c>
@@ -24970,7 +24993,7 @@
         <v>4460</v>
       </c>
     </row>
-    <row r="167" spans="1:21">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>166</v>
       </c>
@@ -25035,7 +25058,7 @@
         <v>4461</v>
       </c>
     </row>
-    <row r="168" spans="1:21">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>167</v>
       </c>
@@ -25100,7 +25123,7 @@
         <v>4462</v>
       </c>
     </row>
-    <row r="169" spans="1:21">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>168</v>
       </c>
@@ -25165,7 +25188,7 @@
         <v>4463</v>
       </c>
     </row>
-    <row r="170" spans="1:21">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>169</v>
       </c>
@@ -25230,7 +25253,7 @@
         <v>4464</v>
       </c>
     </row>
-    <row r="171" spans="1:21">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>170</v>
       </c>
@@ -25295,7 +25318,7 @@
         <v>4465</v>
       </c>
     </row>
-    <row r="172" spans="1:21">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>171</v>
       </c>
@@ -25360,7 +25383,7 @@
         <v>4466</v>
       </c>
     </row>
-    <row r="173" spans="1:21">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>172</v>
       </c>
@@ -25425,7 +25448,7 @@
         <v>4467</v>
       </c>
     </row>
-    <row r="174" spans="1:21">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>173</v>
       </c>
@@ -25490,7 +25513,7 @@
         <v>4468</v>
       </c>
     </row>
-    <row r="175" spans="1:21">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>174</v>
       </c>
@@ -25555,7 +25578,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="176" spans="1:21">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>175</v>
       </c>
@@ -25620,7 +25643,7 @@
         <v>4470</v>
       </c>
     </row>
-    <row r="177" spans="1:21">
+    <row r="177" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>176</v>
       </c>
@@ -25685,7 +25708,7 @@
         <v>4471</v>
       </c>
     </row>
-    <row r="178" spans="1:21">
+    <row r="178" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>177</v>
       </c>
@@ -25750,7 +25773,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="179" spans="1:21">
+    <row r="179" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>178</v>
       </c>
@@ -25815,7 +25838,7 @@
         <v>4473</v>
       </c>
     </row>
-    <row r="180" spans="1:21">
+    <row r="180" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>179</v>
       </c>
@@ -25880,7 +25903,7 @@
         <v>4474</v>
       </c>
     </row>
-    <row r="181" spans="1:21">
+    <row r="181" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>180</v>
       </c>
@@ -25945,7 +25968,7 @@
         <v>4475</v>
       </c>
     </row>
-    <row r="182" spans="1:21">
+    <row r="182" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>181</v>
       </c>
@@ -26010,7 +26033,7 @@
         <v>4476</v>
       </c>
     </row>
-    <row r="183" spans="1:21">
+    <row r="183" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>182</v>
       </c>
@@ -26075,7 +26098,7 @@
         <v>4477</v>
       </c>
     </row>
-    <row r="184" spans="1:21">
+    <row r="184" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>183</v>
       </c>
@@ -26140,7 +26163,7 @@
         <v>4478</v>
       </c>
     </row>
-    <row r="185" spans="1:21">
+    <row r="185" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>184</v>
       </c>
@@ -26205,7 +26228,7 @@
         <v>4479</v>
       </c>
     </row>
-    <row r="186" spans="1:21">
+    <row r="186" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>185</v>
       </c>
@@ -26270,7 +26293,7 @@
         <v>4480</v>
       </c>
     </row>
-    <row r="187" spans="1:21">
+    <row r="187" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>186</v>
       </c>
@@ -26335,7 +26358,7 @@
         <v>4481</v>
       </c>
     </row>
-    <row r="188" spans="1:21">
+    <row r="188" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>187</v>
       </c>
@@ -26400,7 +26423,7 @@
         <v>4482</v>
       </c>
     </row>
-    <row r="189" spans="1:21">
+    <row r="189" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>188</v>
       </c>
@@ -26465,7 +26488,7 @@
         <v>4483</v>
       </c>
     </row>
-    <row r="190" spans="1:21">
+    <row r="190" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>189</v>
       </c>
@@ -26530,7 +26553,7 @@
         <v>4484</v>
       </c>
     </row>
-    <row r="191" spans="1:21">
+    <row r="191" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>190</v>
       </c>
@@ -26595,7 +26618,7 @@
         <v>4485</v>
       </c>
     </row>
-    <row r="192" spans="1:21">
+    <row r="192" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>191</v>
       </c>
@@ -26660,7 +26683,7 @@
         <v>4486</v>
       </c>
     </row>
-    <row r="193" spans="1:21">
+    <row r="193" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>192</v>
       </c>
@@ -26725,7 +26748,7 @@
         <v>4487</v>
       </c>
     </row>
-    <row r="194" spans="1:21">
+    <row r="194" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>193</v>
       </c>
@@ -26790,7 +26813,7 @@
         <v>4488</v>
       </c>
     </row>
-    <row r="195" spans="1:21">
+    <row r="195" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>194</v>
       </c>
@@ -26855,7 +26878,7 @@
         <v>4489</v>
       </c>
     </row>
-    <row r="196" spans="1:21">
+    <row r="196" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>195</v>
       </c>
@@ -26920,7 +26943,7 @@
         <v>4490</v>
       </c>
     </row>
-    <row r="197" spans="1:21">
+    <row r="197" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>196</v>
       </c>
@@ -26985,7 +27008,7 @@
         <v>4491</v>
       </c>
     </row>
-    <row r="198" spans="1:21">
+    <row r="198" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>197</v>
       </c>
@@ -27050,7 +27073,7 @@
         <v>4492</v>
       </c>
     </row>
-    <row r="199" spans="1:21">
+    <row r="199" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>198</v>
       </c>
@@ -27115,7 +27138,7 @@
         <v>4493</v>
       </c>
     </row>
-    <row r="200" spans="1:21">
+    <row r="200" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>199</v>
       </c>
@@ -27180,7 +27203,7 @@
         <v>4494</v>
       </c>
     </row>
-    <row r="201" spans="1:21">
+    <row r="201" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>200</v>
       </c>
@@ -27245,7 +27268,7 @@
         <v>4495</v>
       </c>
     </row>
-    <row r="202" spans="1:21">
+    <row r="202" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>201</v>
       </c>
@@ -27310,7 +27333,7 @@
         <v>4496</v>
       </c>
     </row>
-    <row r="203" spans="1:21">
+    <row r="203" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>202</v>
       </c>
@@ -27375,7 +27398,7 @@
         <v>4497</v>
       </c>
     </row>
-    <row r="204" spans="1:21">
+    <row r="204" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>203</v>
       </c>
@@ -27440,7 +27463,7 @@
         <v>4498</v>
       </c>
     </row>
-    <row r="205" spans="1:21">
+    <row r="205" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>204</v>
       </c>
@@ -27505,7 +27528,7 @@
         <v>4499</v>
       </c>
     </row>
-    <row r="206" spans="1:21">
+    <row r="206" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>205</v>
       </c>
@@ -27570,7 +27593,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="207" spans="1:21">
+    <row r="207" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>206</v>
       </c>
@@ -27635,7 +27658,7 @@
         <v>4501</v>
       </c>
     </row>
-    <row r="208" spans="1:21">
+    <row r="208" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>207</v>
       </c>
@@ -27700,7 +27723,7 @@
         <v>4502</v>
       </c>
     </row>
-    <row r="209" spans="1:21">
+    <row r="209" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>208</v>
       </c>
@@ -27765,7 +27788,7 @@
         <v>4503</v>
       </c>
     </row>
-    <row r="210" spans="1:21">
+    <row r="210" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>209</v>
       </c>
@@ -27830,7 +27853,7 @@
         <v>4504</v>
       </c>
     </row>
-    <row r="211" spans="1:21">
+    <row r="211" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>210</v>
       </c>
@@ -27895,7 +27918,7 @@
         <v>4505</v>
       </c>
     </row>
-    <row r="212" spans="1:21">
+    <row r="212" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>211</v>
       </c>
@@ -27960,7 +27983,7 @@
         <v>4506</v>
       </c>
     </row>
-    <row r="213" spans="1:21">
+    <row r="213" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>212</v>
       </c>
@@ -28025,7 +28048,7 @@
         <v>4507</v>
       </c>
     </row>
-    <row r="214" spans="1:21">
+    <row r="214" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>213</v>
       </c>
@@ -28090,7 +28113,7 @@
         <v>4508</v>
       </c>
     </row>
-    <row r="215" spans="1:21">
+    <row r="215" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>214</v>
       </c>
@@ -28155,7 +28178,7 @@
         <v>4509</v>
       </c>
     </row>
-    <row r="216" spans="1:21">
+    <row r="216" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>215</v>
       </c>
@@ -28220,7 +28243,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="217" spans="1:21">
+    <row r="217" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>216</v>
       </c>
@@ -28285,7 +28308,7 @@
         <v>4511</v>
       </c>
     </row>
-    <row r="218" spans="1:21">
+    <row r="218" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>217</v>
       </c>
@@ -28350,7 +28373,7 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="219" spans="1:21">
+    <row r="219" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>218</v>
       </c>
@@ -28415,7 +28438,7 @@
         <v>4513</v>
       </c>
     </row>
-    <row r="220" spans="1:21">
+    <row r="220" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>219</v>
       </c>
@@ -28480,7 +28503,7 @@
         <v>4514</v>
       </c>
     </row>
-    <row r="221" spans="1:21">
+    <row r="221" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>220</v>
       </c>
@@ -28545,7 +28568,7 @@
         <v>4515</v>
       </c>
     </row>
-    <row r="222" spans="1:21">
+    <row r="222" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>221</v>
       </c>
@@ -28610,7 +28633,7 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="223" spans="1:21">
+    <row r="223" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>222</v>
       </c>
@@ -28675,7 +28698,7 @@
         <v>4499</v>
       </c>
     </row>
-    <row r="224" spans="1:21">
+    <row r="224" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>223</v>
       </c>
@@ -28740,7 +28763,7 @@
         <v>4516</v>
       </c>
     </row>
-    <row r="225" spans="1:21">
+    <row r="225" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>224</v>
       </c>
@@ -28805,7 +28828,7 @@
         <v>4517</v>
       </c>
     </row>
-    <row r="226" spans="1:21">
+    <row r="226" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>225</v>
       </c>
@@ -28870,7 +28893,7 @@
         <v>4518</v>
       </c>
     </row>
-    <row r="227" spans="1:21">
+    <row r="227" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>226</v>
       </c>
@@ -28935,7 +28958,7 @@
         <v>4519</v>
       </c>
     </row>
-    <row r="228" spans="1:21">
+    <row r="228" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>227</v>
       </c>
@@ -29000,7 +29023,7 @@
         <v>4520</v>
       </c>
     </row>
-    <row r="229" spans="1:21">
+    <row r="229" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>228</v>
       </c>
@@ -29065,7 +29088,7 @@
         <v>4521</v>
       </c>
     </row>
-    <row r="230" spans="1:21">
+    <row r="230" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>229</v>
       </c>
@@ -29130,7 +29153,7 @@
         <v>4522</v>
       </c>
     </row>
-    <row r="231" spans="1:21">
+    <row r="231" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>230</v>
       </c>
@@ -29195,7 +29218,7 @@
         <v>4523</v>
       </c>
     </row>
-    <row r="232" spans="1:21">
+    <row r="232" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>231</v>
       </c>
@@ -29260,7 +29283,7 @@
         <v>4524</v>
       </c>
     </row>
-    <row r="233" spans="1:21">
+    <row r="233" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>232</v>
       </c>
@@ -29325,7 +29348,7 @@
         <v>4525</v>
       </c>
     </row>
-    <row r="234" spans="1:21">
+    <row r="234" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>233</v>
       </c>
@@ -29390,7 +29413,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="235" spans="1:21">
+    <row r="235" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>234</v>
       </c>
@@ -29455,7 +29478,7 @@
         <v>4527</v>
       </c>
     </row>
-    <row r="236" spans="1:21">
+    <row r="236" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>235</v>
       </c>
@@ -29520,7 +29543,7 @@
         <v>4528</v>
       </c>
     </row>
-    <row r="237" spans="1:21">
+    <row r="237" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>236</v>
       </c>
@@ -29585,7 +29608,7 @@
         <v>4529</v>
       </c>
     </row>
-    <row r="238" spans="1:21">
+    <row r="238" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>237</v>
       </c>
@@ -29650,7 +29673,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="239" spans="1:21">
+    <row r="239" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>238</v>
       </c>
@@ -29715,7 +29738,7 @@
         <v>4525</v>
       </c>
     </row>
-    <row r="240" spans="1:21">
+    <row r="240" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>239</v>
       </c>
@@ -29780,7 +29803,7 @@
         <v>4531</v>
       </c>
     </row>
-    <row r="241" spans="1:21">
+    <row r="241" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>240</v>
       </c>
@@ -29845,7 +29868,7 @@
         <v>4532</v>
       </c>
     </row>
-    <row r="242" spans="1:21">
+    <row r="242" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>241</v>
       </c>
@@ -29910,7 +29933,7 @@
         <v>4533</v>
       </c>
     </row>
-    <row r="243" spans="1:21">
+    <row r="243" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>242</v>
       </c>
@@ -29975,7 +29998,7 @@
         <v>4534</v>
       </c>
     </row>
-    <row r="244" spans="1:21">
+    <row r="244" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>243</v>
       </c>
@@ -30040,7 +30063,7 @@
         <v>4535</v>
       </c>
     </row>
-    <row r="245" spans="1:21">
+    <row r="245" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>244</v>
       </c>
@@ -30105,7 +30128,7 @@
         <v>4536</v>
       </c>
     </row>
-    <row r="246" spans="1:21">
+    <row r="246" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>245</v>
       </c>
@@ -30170,7 +30193,7 @@
         <v>4537</v>
       </c>
     </row>
-    <row r="247" spans="1:21">
+    <row r="247" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>246</v>
       </c>
@@ -30235,7 +30258,7 @@
         <v>4538</v>
       </c>
     </row>
-    <row r="248" spans="1:21">
+    <row r="248" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>247</v>
       </c>
@@ -30300,7 +30323,7 @@
         <v>4539</v>
       </c>
     </row>
-    <row r="249" spans="1:21">
+    <row r="249" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>248</v>
       </c>
@@ -30365,7 +30388,7 @@
         <v>4540</v>
       </c>
     </row>
-    <row r="250" spans="1:21">
+    <row r="250" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>249</v>
       </c>
@@ -30430,7 +30453,7 @@
         <v>4541</v>
       </c>
     </row>
-    <row r="251" spans="1:21">
+    <row r="251" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>250</v>
       </c>
@@ -30495,7 +30518,7 @@
         <v>4542</v>
       </c>
     </row>
-    <row r="252" spans="1:21">
+    <row r="252" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>251</v>
       </c>
@@ -30560,7 +30583,7 @@
         <v>4543</v>
       </c>
     </row>
-    <row r="253" spans="1:21">
+    <row r="253" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>252</v>
       </c>
@@ -30625,7 +30648,7 @@
         <v>4544</v>
       </c>
     </row>
-    <row r="254" spans="1:21">
+    <row r="254" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>253</v>
       </c>
@@ -30690,7 +30713,7 @@
         <v>4545</v>
       </c>
     </row>
-    <row r="255" spans="1:21">
+    <row r="255" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>254</v>
       </c>
@@ -30755,7 +30778,7 @@
         <v>4546</v>
       </c>
     </row>
-    <row r="256" spans="1:21">
+    <row r="256" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>255</v>
       </c>
@@ -30820,7 +30843,7 @@
         <v>4547</v>
       </c>
     </row>
-    <row r="257" spans="1:21">
+    <row r="257" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>256</v>
       </c>
@@ -30885,7 +30908,7 @@
         <v>4548</v>
       </c>
     </row>
-    <row r="258" spans="1:21">
+    <row r="258" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>257</v>
       </c>
@@ -30950,7 +30973,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="259" spans="1:21">
+    <row r="259" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>258</v>
       </c>
@@ -31015,7 +31038,7 @@
         <v>4550</v>
       </c>
     </row>
-    <row r="260" spans="1:21">
+    <row r="260" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>259</v>
       </c>
@@ -31080,7 +31103,7 @@
         <v>4551</v>
       </c>
     </row>
-    <row r="261" spans="1:21">
+    <row r="261" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>260</v>
       </c>
@@ -31145,7 +31168,7 @@
         <v>4552</v>
       </c>
     </row>
-    <row r="262" spans="1:21">
+    <row r="262" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>261</v>
       </c>
@@ -31210,7 +31233,7 @@
         <v>4553</v>
       </c>
     </row>
-    <row r="263" spans="1:21">
+    <row r="263" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>262</v>
       </c>
@@ -31275,7 +31298,7 @@
         <v>4554</v>
       </c>
     </row>
-    <row r="264" spans="1:21">
+    <row r="264" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>263</v>
       </c>
@@ -31340,7 +31363,7 @@
         <v>4555</v>
       </c>
     </row>
-    <row r="265" spans="1:21">
+    <row r="265" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>264</v>
       </c>
@@ -31405,7 +31428,7 @@
         <v>4556</v>
       </c>
     </row>
-    <row r="266" spans="1:21">
+    <row r="266" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>265</v>
       </c>
@@ -31470,7 +31493,7 @@
         <v>4557</v>
       </c>
     </row>
-    <row r="267" spans="1:21">
+    <row r="267" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>266</v>
       </c>
@@ -31535,7 +31558,7 @@
         <v>4558</v>
       </c>
     </row>
-    <row r="268" spans="1:21">
+    <row r="268" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>267</v>
       </c>
@@ -31600,7 +31623,7 @@
         <v>4559</v>
       </c>
     </row>
-    <row r="269" spans="1:21">
+    <row r="269" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>268</v>
       </c>
@@ -31665,7 +31688,7 @@
         <v>4560</v>
       </c>
     </row>
-    <row r="270" spans="1:21">
+    <row r="270" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>269</v>
       </c>
@@ -31730,7 +31753,7 @@
         <v>4561</v>
       </c>
     </row>
-    <row r="271" spans="1:21">
+    <row r="271" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>270</v>
       </c>
@@ -31795,7 +31818,7 @@
         <v>4562</v>
       </c>
     </row>
-    <row r="272" spans="1:21">
+    <row r="272" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>271</v>
       </c>
@@ -31860,7 +31883,7 @@
         <v>4563</v>
       </c>
     </row>
-    <row r="273" spans="1:21">
+    <row r="273" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>272</v>
       </c>
@@ -31925,7 +31948,7 @@
         <v>4564</v>
       </c>
     </row>
-    <row r="274" spans="1:21">
+    <row r="274" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>273</v>
       </c>
@@ -31990,7 +32013,7 @@
         <v>4565</v>
       </c>
     </row>
-    <row r="275" spans="1:21">
+    <row r="275" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>274</v>
       </c>
@@ -32055,7 +32078,7 @@
         <v>4566</v>
       </c>
     </row>
-    <row r="276" spans="1:21">
+    <row r="276" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>275</v>
       </c>
@@ -32120,7 +32143,7 @@
         <v>4567</v>
       </c>
     </row>
-    <row r="277" spans="1:21">
+    <row r="277" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>276</v>
       </c>
@@ -32185,7 +32208,7 @@
         <v>4568</v>
       </c>
     </row>
-    <row r="278" spans="1:21">
+    <row r="278" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>277</v>
       </c>
@@ -32250,7 +32273,7 @@
         <v>4569</v>
       </c>
     </row>
-    <row r="279" spans="1:21">
+    <row r="279" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>278</v>
       </c>
@@ -32315,7 +32338,7 @@
         <v>4570</v>
       </c>
     </row>
-    <row r="280" spans="1:21">
+    <row r="280" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>279</v>
       </c>
@@ -32380,7 +32403,7 @@
         <v>4571</v>
       </c>
     </row>
-    <row r="281" spans="1:21">
+    <row r="281" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>280</v>
       </c>
@@ -32445,7 +32468,7 @@
         <v>4572</v>
       </c>
     </row>
-    <row r="282" spans="1:21">
+    <row r="282" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>281</v>
       </c>
@@ -32510,7 +32533,7 @@
         <v>4573</v>
       </c>
     </row>
-    <row r="283" spans="1:21">
+    <row r="283" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>282</v>
       </c>
@@ -32575,7 +32598,7 @@
         <v>4574</v>
       </c>
     </row>
-    <row r="284" spans="1:21">
+    <row r="284" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>283</v>
       </c>
@@ -32640,7 +32663,7 @@
         <v>4575</v>
       </c>
     </row>
-    <row r="285" spans="1:21">
+    <row r="285" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>284</v>
       </c>
@@ -32705,7 +32728,7 @@
         <v>4576</v>
       </c>
     </row>
-    <row r="286" spans="1:21">
+    <row r="286" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>285</v>
       </c>
@@ -32770,7 +32793,7 @@
         <v>4577</v>
       </c>
     </row>
-    <row r="287" spans="1:21">
+    <row r="287" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>286</v>
       </c>
@@ -32835,7 +32858,7 @@
         <v>4578</v>
       </c>
     </row>
-    <row r="288" spans="1:21">
+    <row r="288" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>287</v>
       </c>
@@ -32900,7 +32923,7 @@
         <v>4579</v>
       </c>
     </row>
-    <row r="289" spans="1:21">
+    <row r="289" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>288</v>
       </c>
@@ -32965,7 +32988,7 @@
         <v>4580</v>
       </c>
     </row>
-    <row r="290" spans="1:21">
+    <row r="290" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>289</v>
       </c>
@@ -33030,7 +33053,7 @@
         <v>4581</v>
       </c>
     </row>
-    <row r="291" spans="1:21">
+    <row r="291" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>290</v>
       </c>
@@ -33095,7 +33118,7 @@
         <v>4582</v>
       </c>
     </row>
-    <row r="292" spans="1:21">
+    <row r="292" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>291</v>
       </c>
@@ -33160,7 +33183,7 @@
         <v>4583</v>
       </c>
     </row>
-    <row r="293" spans="1:21">
+    <row r="293" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>292</v>
       </c>
@@ -33225,7 +33248,7 @@
         <v>4584</v>
       </c>
     </row>
-    <row r="294" spans="1:21">
+    <row r="294" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>293</v>
       </c>
@@ -33290,7 +33313,7 @@
         <v>4585</v>
       </c>
     </row>
-    <row r="295" spans="1:21">
+    <row r="295" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>294</v>
       </c>
@@ -33355,7 +33378,7 @@
         <v>4586</v>
       </c>
     </row>
-    <row r="296" spans="1:21">
+    <row r="296" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>295</v>
       </c>
@@ -33420,7 +33443,7 @@
         <v>4587</v>
       </c>
     </row>
-    <row r="297" spans="1:21">
+    <row r="297" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>296</v>
       </c>
@@ -33485,7 +33508,7 @@
         <v>4588</v>
       </c>
     </row>
-    <row r="298" spans="1:21">
+    <row r="298" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>297</v>
       </c>
@@ -33550,7 +33573,7 @@
         <v>4589</v>
       </c>
     </row>
-    <row r="299" spans="1:21">
+    <row r="299" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>298</v>
       </c>
@@ -33615,7 +33638,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="300" spans="1:21">
+    <row r="300" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>299</v>
       </c>
@@ -33680,7 +33703,7 @@
         <v>4591</v>
       </c>
     </row>
-    <row r="301" spans="1:21">
+    <row r="301" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>300</v>
       </c>
@@ -33745,7 +33768,7 @@
         <v>4592</v>
       </c>
     </row>
-    <row r="302" spans="1:21">
+    <row r="302" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>301</v>
       </c>
@@ -33810,7 +33833,7 @@
         <v>4593</v>
       </c>
     </row>
-    <row r="303" spans="1:21">
+    <row r="303" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>302</v>
       </c>
@@ -33875,7 +33898,7 @@
         <v>4594</v>
       </c>
     </row>
-    <row r="304" spans="1:21">
+    <row r="304" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>303</v>
       </c>
@@ -33940,7 +33963,7 @@
         <v>4595</v>
       </c>
     </row>
-    <row r="305" spans="1:21">
+    <row r="305" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>304</v>
       </c>
@@ -34005,7 +34028,7 @@
         <v>4596</v>
       </c>
     </row>
-    <row r="306" spans="1:21">
+    <row r="306" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>305</v>
       </c>
@@ -34070,7 +34093,7 @@
         <v>4597</v>
       </c>
     </row>
-    <row r="307" spans="1:21">
+    <row r="307" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>306</v>
       </c>
@@ -34135,7 +34158,7 @@
         <v>4598</v>
       </c>
     </row>
-    <row r="308" spans="1:21">
+    <row r="308" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>307</v>
       </c>
@@ -34200,7 +34223,7 @@
         <v>4596</v>
       </c>
     </row>
-    <row r="309" spans="1:21">
+    <row r="309" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>308</v>
       </c>
@@ -34265,7 +34288,7 @@
         <v>4599</v>
       </c>
     </row>
-    <row r="310" spans="1:21">
+    <row r="310" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>309</v>
       </c>
@@ -34330,7 +34353,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="311" spans="1:21">
+    <row r="311" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>310</v>
       </c>
@@ -34397,5 +34420,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>